--- a/test/off.xlsx
+++ b/test/off.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6342D87-70C6-45B7-9E8D-9D3C260C03B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E04C05C-9B78-4093-AF95-114EFDFDC446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>branch</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
@@ -43,12 +40,6 @@
     <t>country</t>
   </si>
   <si>
-    <t>Mumbai Branch</t>
-  </si>
-  <si>
-    <t>Andheri</t>
-  </si>
-  <si>
     <t>101 Andheri East, Mumbai</t>
   </si>
   <si>
@@ -59,13 +50,22 @@
   </si>
   <si>
     <t>India</t>
+  </si>
+  <si>
+    <t>Branch_name</t>
+  </si>
+  <si>
+    <t>Malad</t>
+  </si>
+  <si>
+    <t>Malvani</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +77,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -431,51 +437,52 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>9876543210</v>
       </c>
       <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test/off.xlsx
+++ b/test/off.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E04C05C-9B78-4093-AF95-114EFDFDC446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFEC2CE-0B48-4C43-93F8-22FA358671DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>location</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>Malvani</t>
+  </si>
+  <si>
+    <t>102 Andheri East, Mumbai</t>
   </si>
 </sst>
 </file>
@@ -432,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -466,7 +469,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>9876543210</v>
+        <v>987654</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -478,6 +481,29 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <v>9876543210</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
     </row>
